--- a/output/(山本)規範適合性_制約適合性_再構成.xlsx
+++ b/output/(山本)規範適合性_制約適合性_再構成.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26.13" customWidth="1" min="1" max="1"/>
@@ -461,51 +461,33 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>業務ドメインで定義されるデータの型、有効な値の範囲、および精度について、関連する法令やJIS規格等の外部制約を網羅して記述している。</t>
+          <t>対象業務に適用される法令や業界標準に基づき、取り扱うデータの定義域（有効範囲）、保護要件、および処理可能容量の限界値を、データ要件定義書等の設計ドキュメントに明記している。</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>★新規追加
-【非適合例】個人情報の氏名属性について、最大文字数や許容する文字種、およびサロゲートペア等の扱いを定義せずに設計を進めている。(業界標準に基づくデータ定義が不足し、文字化け等の不具合の要因となるため）
-→【適合例】個人情報の氏名属性に対し、JIS X 0213等の規格に基づいた許容文字種と、最大50文字の制約をデータ定義書に明記し、DB設計に反映している。</t>
+【非適合例】個人データの保存先データベースについて、データ保護に関する具体的な仕様を記載していない。（法的制約を考慮した保護要件が不明確であり、実装の拠り所とならないため。）
+→【適合例】個人データの保存先テーブル定義について、個人情報保護法のガイドラインに準拠し、該当カラムを暗号化して保存するとともに、画面表示時はマスキング処理を適用する旨を明記している。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>ドメインで扱うデータの定義域、処理可能容量などが適切である</t>
+          <t>開発制約として対象言語の書記体系に適合している</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>想定される最大データ蓄積量、最大同時接続数、およびバックアップの保持期間を、業務の実態や処理ピーク時の負荷予測に基づいて具体的に定義している。</t>
+          <t>対象言語特有の書記体系（右横書きなど）や文字コードの制約に基づき、UIコンポーネントの配置規則、文字の折り返し位置、および入力文字数制限をUI設計書に明記している。</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>★新規追加
-【非適合例】1日あたりのトランザクション最大件数を定義せず、根拠なく標準的なサーバ構成を前提としている。(処理可能容量の制約が不明確であり、高負荷時の動作を保証できないため）
-→【適合例】実業務の統計データに基づき、ピーク時の1時間あたり最大1万件のトランザクションを遅延なく処理できる処理容量の制約を、非機能要件として明記している。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>開発制約として対象言語の書記体系に適合している</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>ユーザーインターフェースや帳票の設計において、対象言語特有の書字方向（RTL等）、使用可能な文字セット、および禁則処理等の書記体系上の規則を要件として定義している。</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>【非適合例】アラビア語対応の画面設計において、左から右へ読む標準的なレイアウトをそのまま流用している。(右横書きの言語仕様であるRTLに対応していないため）
-→【適合例】アラビア語版の画面設計において、書字方向に適合するようにメニューや入力項目の配置を左右反転させたRTL（Right-to-Left）レイアウトを定義している。</t>
+【非適合例】アラビア語版の画面設計において、他の言語と同様に左からの文字入力および左揃えのレイアウトとして設計している。（右横書きという対象言語特有の書記体系から逸脱しているため。）
+→【適合例】アラビア語版の画面設計において、対象言語の仕様に基づきRTL（Right-to-Left）属性を適用し、右からの文字入力および右揃えのレイアウトとする旨を明記している。</t>
         </is>
       </c>
     </row>
